--- a/Renda_por_Divisao_CNAE_RAIS_Ananindeua.xlsx
+++ b/Renda_por_Divisao_CNAE_RAIS_Ananindeua.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -450,121 +450,86 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Nome Seção</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Divisão</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Nome Divisão</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Renda Média Ananindeua (R$)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Vínculos Ananindeua</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Renda Média Pará (R$)</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Vínculos Pará</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>QL Renda (Ana/Pa)</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AGRICULTURA, PECUÁRIA E SERVIÇOS RELACIONADOS</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1873.45</v>
-      </c>
-      <c r="F4" t="n">
-        <v>129</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2635.197144</v>
-      </c>
-      <c r="H4" t="n">
-        <v>104286</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.710934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
+          <t>AGRICULTURA, PECUÁRIA E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2677.349684</v>
+        <v>1873.45</v>
       </c>
       <c r="F5" t="n">
-        <v>4242</v>
+        <v>129</v>
       </c>
       <c r="G5" t="n">
-        <v>2641.254964</v>
+        <v>2635.197144</v>
       </c>
       <c r="H5" t="n">
-        <v>89228</v>
+        <v>104286</v>
       </c>
       <c r="I5" t="n">
-        <v>1.013666</v>
+        <v>0.710934</v>
       </c>
     </row>
     <row r="6">
@@ -579,27 +544,27 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE BEBIDAS</t>
+          <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2545.100909</v>
+        <v>2677.349684</v>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>4242</v>
       </c>
       <c r="G6" t="n">
-        <v>3206.446996</v>
+        <v>2641.254964</v>
       </c>
       <c r="H6" t="n">
-        <v>8273</v>
+        <v>89228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.793745</v>
+        <v>1.013666</v>
       </c>
     </row>
     <row r="7">
@@ -614,27 +579,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
+          <t>FABRICAÇÃO DE BEBIDAS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1809.07</v>
+        <v>2545.100909</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="G7" t="n">
-        <v>2084.118844</v>
+        <v>3206.446996</v>
       </c>
       <c r="H7" t="n">
-        <v>2648</v>
+        <v>8273</v>
       </c>
       <c r="I7" t="n">
-        <v>0.868026</v>
+        <v>0.793745</v>
       </c>
     </row>
     <row r="8">
@@ -649,27 +614,27 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1865.38442</v>
+        <v>1809.07</v>
       </c>
       <c r="F8" t="n">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>1828.820862</v>
+        <v>2084.118844</v>
       </c>
       <c r="H8" t="n">
-        <v>4395</v>
+        <v>2648</v>
       </c>
       <c r="I8" t="n">
-        <v>1.019993</v>
+        <v>0.868026</v>
       </c>
     </row>
     <row r="9">
@@ -684,27 +649,27 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
+          <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1733.88</v>
+        <v>1865.38442</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="G9" t="n">
-        <v>2605.352094</v>
+        <v>1828.820862</v>
       </c>
       <c r="H9" t="n">
-        <v>3476</v>
+        <v>4395</v>
       </c>
       <c r="I9" t="n">
-        <v>0.665507</v>
+        <v>1.019993</v>
       </c>
     </row>
     <row r="10">
@@ -719,27 +684,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
+          <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3087.425007</v>
+        <v>1733.88</v>
       </c>
       <c r="F10" t="n">
-        <v>701</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2492.016059</v>
+        <v>2605.352094</v>
       </c>
       <c r="H10" t="n">
-        <v>14538</v>
+        <v>3476</v>
       </c>
       <c r="I10" t="n">
-        <v>1.238927</v>
+        <v>0.665507</v>
       </c>
     </row>
     <row r="11">
@@ -754,27 +719,27 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE CELULOSE, PAPEL E PRODUTOS DE PAPEL</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2275.328696</v>
+        <v>3087.425007</v>
       </c>
       <c r="F11" t="n">
-        <v>92</v>
+        <v>701</v>
       </c>
       <c r="G11" t="n">
-        <v>3289.228769</v>
+        <v>2492.016059</v>
       </c>
       <c r="H11" t="n">
-        <v>5247</v>
+        <v>14538</v>
       </c>
       <c r="I11" t="n">
-        <v>0.691751</v>
+        <v>1.238927</v>
       </c>
     </row>
     <row r="12">
@@ -789,27 +754,27 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
+          <t>FABRICAÇÃO DE CELULOSE, PAPEL E PRODUTOS DE PAPEL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1964.900385</v>
+        <v>2275.328696</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="G12" t="n">
-        <v>2243.437741</v>
+        <v>3289.228769</v>
       </c>
       <c r="H12" t="n">
-        <v>3595</v>
+        <v>5247</v>
       </c>
       <c r="I12" t="n">
-        <v>0.875844</v>
+        <v>0.691751</v>
       </c>
     </row>
     <row r="13">
@@ -824,97 +789,97 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE COQUE, DE PRODUTOS DERIVADOS DO PETRÓLEO E DE BIOCOMBUSTÍVEIS</t>
+          <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3290.996721</v>
+        <v>1964.900385</v>
       </c>
       <c r="F13" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>4089.675863</v>
+        <v>2243.437741</v>
       </c>
       <c r="H13" t="n">
-        <v>3979</v>
+        <v>3595</v>
       </c>
       <c r="I13" t="n">
-        <v>0.804708</v>
+        <v>0.875844</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PRODUÇÃO FLORESTAL</t>
+          <t>FABRICAÇÃO DE COQUE, DE PRODUTOS DERIVADOS DO PETRÓLEO E DE BIOCOMBUSTÍVEIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4757.2</v>
+        <v>3290.996721</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="G14" t="n">
-        <v>2911.558271</v>
+        <v>4089.675863</v>
       </c>
       <c r="H14" t="n">
-        <v>7594</v>
+        <v>3979</v>
       </c>
       <c r="I14" t="n">
-        <v>1.633902</v>
+        <v>0.804708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
+          <t>PRODUÇÃO FLORESTAL</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2613.732805</v>
+        <v>4757.2</v>
       </c>
       <c r="F15" t="n">
-        <v>688</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>3660.913293</v>
+        <v>2911.558271</v>
       </c>
       <c r="H15" t="n">
-        <v>8229</v>
+        <v>7594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.713956</v>
+        <v>1.633902</v>
       </c>
     </row>
     <row r="16">
@@ -929,31 +894,27 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS FARMOQUÍMICOS E FARMACÊUTICOS</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2613.732805</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="G16" t="n">
-        <v>4664.245892</v>
+        <v>3660.913293</v>
       </c>
       <c r="H16" t="n">
-        <v>1346</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>8229</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.713956</v>
       </c>
     </row>
     <row r="17">
@@ -968,27 +929,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE BORRACHA E DE MATERIAL PLÁSTICO</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2651.106931</v>
+          <t>FABRICAÇÃO DE PRODUTOS FARMOQUÍMICOS E FARMACÊUTICOS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3375.698749</v>
+        <v>4664.245892</v>
       </c>
       <c r="H17" t="n">
-        <v>18289</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.785351</v>
+        <v>1346</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1003,27 +968,27 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE BORRACHA E DE MATERIAL PLÁSTICO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2723.266048</v>
+        <v>2651.106931</v>
       </c>
       <c r="F18" t="n">
-        <v>792</v>
+        <v>492</v>
       </c>
       <c r="G18" t="n">
-        <v>2485.562422</v>
+        <v>3375.698749</v>
       </c>
       <c r="H18" t="n">
-        <v>17071</v>
+        <v>18289</v>
       </c>
       <c r="I18" t="n">
-        <v>1.095634</v>
+        <v>0.785351</v>
       </c>
     </row>
     <row r="19">
@@ -1038,27 +1003,27 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>METALURGIA</t>
+          <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2439.49513</v>
+        <v>2723.266048</v>
       </c>
       <c r="F19" t="n">
-        <v>154</v>
+        <v>792</v>
       </c>
       <c r="G19" t="n">
-        <v>5491.600103</v>
+        <v>2485.562422</v>
       </c>
       <c r="H19" t="n">
-        <v>12798</v>
+        <v>17071</v>
       </c>
       <c r="I19" t="n">
-        <v>0.444223</v>
+        <v>1.095634</v>
       </c>
     </row>
     <row r="20">
@@ -1073,27 +1038,27 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
+          <t>METALURGIA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2650.480317</v>
+        <v>2439.49513</v>
       </c>
       <c r="F20" t="n">
-        <v>221</v>
+        <v>154</v>
       </c>
       <c r="G20" t="n">
-        <v>3316.442745</v>
+        <v>5491.600103</v>
       </c>
       <c r="H20" t="n">
-        <v>13382</v>
+        <v>12798</v>
       </c>
       <c r="I20" t="n">
-        <v>0.799194</v>
+        <v>0.444223</v>
       </c>
     </row>
     <row r="21">
@@ -1108,31 +1073,27 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE EQUIPAMENTOS DE INFORMÁTICA, PRODUTOS ELETRÔNICOS E ÓPTICOS</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2650.480317</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="G21" t="n">
-        <v>3941.304626</v>
+        <v>3316.442745</v>
       </c>
       <c r="H21" t="n">
-        <v>30374</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>13382</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.799194</v>
       </c>
     </row>
     <row r="22">
@@ -1147,27 +1108,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÁQUINAS, APARELHOS E MATERIAIS ELÉTRICOS</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2313.619589</v>
+          <t>FABRICAÇÃO DE EQUIPAMENTOS DE INFORMÁTICA, PRODUTOS ELETRÔNICOS E ÓPTICOS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3466.873835</v>
+        <v>3941.304626</v>
       </c>
       <c r="H22" t="n">
-        <v>8352</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.66735</v>
+        <v>30374</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1182,27 +1147,27 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE MÁQUINAS, APARELHOS E MATERIAIS ELÉTRICOS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3176.86025</v>
+        <v>2313.619589</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="G23" t="n">
-        <v>3972.233063</v>
+        <v>3466.873835</v>
       </c>
       <c r="H23" t="n">
-        <v>8459</v>
+        <v>8352</v>
       </c>
       <c r="I23" t="n">
-        <v>0.799767</v>
+        <v>0.66735</v>
       </c>
     </row>
     <row r="24">
@@ -1217,101 +1182,101 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
+          <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2217.898235</v>
+        <v>3176.86025</v>
       </c>
       <c r="F24" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>3454.059563</v>
+        <v>3972.233063</v>
       </c>
       <c r="H24" t="n">
-        <v>7374</v>
+        <v>8459</v>
       </c>
       <c r="I24" t="n">
-        <v>0.642113</v>
+        <v>0.799767</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PESCA E AQÜICULTURA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2217.898235</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G25" t="n">
-        <v>2344.143184</v>
+        <v>3454.059563</v>
       </c>
       <c r="H25" t="n">
-        <v>1052</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7374</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.642113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE OUTROS EQUIPAMENTOS DE TRANSPORTE, EXCETO VEÍCULOS AUTOMOTORES</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>3150.448</v>
+          <t>PESCA E AQÜICULTURA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5135.769229</v>
+        <v>2344.143184</v>
       </c>
       <c r="H26" t="n">
-        <v>24526</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.613433</v>
+        <v>1052</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1326,27 +1291,27 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE MÓVEIS</t>
+          <t>FABRICAÇÃO DE OUTROS EQUIPAMENTOS DE TRANSPORTE, EXCETO VEÍCULOS AUTOMOTORES</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2155.502051</v>
+        <v>3150.448</v>
       </c>
       <c r="F27" t="n">
-        <v>590</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>2475.036147</v>
+        <v>5135.769229</v>
       </c>
       <c r="H27" t="n">
-        <v>6553</v>
+        <v>24526</v>
       </c>
       <c r="I27" t="n">
-        <v>0.870897</v>
+        <v>0.613433</v>
       </c>
     </row>
     <row r="28">
@@ -1361,27 +1326,27 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
+          <t>FABRICAÇÃO DE MÓVEIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1850.134545</v>
+        <v>2155.502051</v>
       </c>
       <c r="F28" t="n">
-        <v>121</v>
+        <v>590</v>
       </c>
       <c r="G28" t="n">
-        <v>2907.595459</v>
+        <v>2475.036147</v>
       </c>
       <c r="H28" t="n">
-        <v>4787</v>
+        <v>6553</v>
       </c>
       <c r="I28" t="n">
-        <v>0.636311</v>
+        <v>0.870897</v>
       </c>
     </row>
     <row r="29">
@@ -1396,101 +1361,101 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+          <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2754.15576</v>
+        <v>1850.134545</v>
       </c>
       <c r="F29" t="n">
-        <v>500</v>
+        <v>121</v>
       </c>
       <c r="G29" t="n">
-        <v>3161.418785</v>
+        <v>2907.595459</v>
       </c>
       <c r="H29" t="n">
-        <v>12605</v>
+        <v>4787</v>
       </c>
       <c r="I29" t="n">
-        <v>0.871177</v>
+        <v>0.636311</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ELETRICIDADE E GÁS</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2754.15576</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G30" t="n">
-        <v>6811.088797</v>
+        <v>3161.418785</v>
       </c>
       <c r="H30" t="n">
-        <v>12905</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>12605</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.871177</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
+          <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAPTAÇÃO, TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>2536.292381</v>
+          <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4759.262345</v>
+        <v>6811.088797</v>
       </c>
       <c r="H31" t="n">
-        <v>10441</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.532917</v>
+        <v>12905</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1505,27 +1470,27 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ESGOTO E ATIVIDADES RELACIONADAS</t>
+          <t>CAPTAÇÃO, TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2802.474118</v>
+        <v>2536.292381</v>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G32" t="n">
-        <v>2640.627046</v>
+        <v>4759.262345</v>
       </c>
       <c r="H32" t="n">
-        <v>457</v>
+        <v>10441</v>
       </c>
       <c r="I32" t="n">
-        <v>1.061291</v>
+        <v>0.532917</v>
       </c>
     </row>
     <row r="33">
@@ -1540,27 +1505,27 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
+          <t>ESGOTO E ATIVIDADES RELACIONADAS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2763.048652</v>
+        <v>2802.474118</v>
       </c>
       <c r="F33" t="n">
-        <v>1328</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>2728.160887</v>
+        <v>2640.627046</v>
       </c>
       <c r="H33" t="n">
-        <v>10973</v>
+        <v>457</v>
       </c>
       <c r="I33" t="n">
-        <v>1.012788</v>
+        <v>1.061291</v>
       </c>
     </row>
     <row r="34">
@@ -1575,66 +1540,66 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DESCONTAMINAÇÃO E OUTROS SERVIÇOS DE GESTÃO DE RESÍDUOS</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2763.048652</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1328</v>
       </c>
       <c r="G34" t="n">
-        <v>2330.951111</v>
+        <v>2728.160887</v>
       </c>
       <c r="H34" t="n">
-        <v>27</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10973</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.012788</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO</t>
+          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>2217.128974</v>
+          <t>DESCONTAMINAÇÃO E OUTROS SERVIÇOS DE GESTÃO DE RESÍDUOS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>1667</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2478.15883</v>
+        <v>2330.951111</v>
       </c>
       <c r="H35" t="n">
-        <v>53041</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.894668</v>
+        <v>27</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1649,27 +1614,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OBRAS DE INFRA-ESTRUTURA</t>
+          <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3611.458028</v>
+        <v>2217.128974</v>
       </c>
       <c r="F36" t="n">
-        <v>2099</v>
+        <v>1667</v>
       </c>
       <c r="G36" t="n">
-        <v>3563.770881</v>
+        <v>2478.15883</v>
       </c>
       <c r="H36" t="n">
-        <v>59348</v>
+        <v>53041</v>
       </c>
       <c r="I36" t="n">
-        <v>1.013381</v>
+        <v>0.894668</v>
       </c>
     </row>
     <row r="37">
@@ -1684,62 +1649,62 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
+          <t>OBRAS DE INFRA-ESTRUTURA</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2471.714245</v>
+        <v>3611.458028</v>
       </c>
       <c r="F37" t="n">
-        <v>742</v>
+        <v>2099</v>
       </c>
       <c r="G37" t="n">
-        <v>2871.449377</v>
+        <v>3563.770881</v>
       </c>
       <c r="H37" t="n">
-        <v>45112</v>
+        <v>59348</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8607900000000001</v>
+        <v>1.013381</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3351.357196</v>
+        <v>2471.714245</v>
       </c>
       <c r="F38" t="n">
-        <v>3278</v>
+        <v>742</v>
       </c>
       <c r="G38" t="n">
-        <v>3029.790097</v>
+        <v>2871.449377</v>
       </c>
       <c r="H38" t="n">
-        <v>69231</v>
+        <v>45112</v>
       </c>
       <c r="I38" t="n">
-        <v>1.106135</v>
+        <v>0.8607900000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1754,27 +1719,27 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3010.494691</v>
+        <v>3351.357196</v>
       </c>
       <c r="F39" t="n">
-        <v>5133</v>
+        <v>3278</v>
       </c>
       <c r="G39" t="n">
-        <v>2935.297564</v>
+        <v>3029.790097</v>
       </c>
       <c r="H39" t="n">
-        <v>109578</v>
+        <v>69231</v>
       </c>
       <c r="I39" t="n">
-        <v>1.025618</v>
+        <v>1.106135</v>
       </c>
     </row>
     <row r="40">
@@ -1789,62 +1754,62 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>COMÉRCIO VAREJISTA</t>
+          <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2187.730908</v>
+        <v>3010.494691</v>
       </c>
       <c r="F40" t="n">
-        <v>13682</v>
+        <v>5133</v>
       </c>
       <c r="G40" t="n">
-        <v>2208.89971</v>
+        <v>2935.297564</v>
       </c>
       <c r="H40" t="n">
-        <v>430083</v>
+        <v>109578</v>
       </c>
       <c r="I40" t="n">
-        <v>0.990417</v>
+        <v>1.025618</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
+          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TRANSPORTE TERRESTRE</t>
+          <t>COMÉRCIO VAREJISTA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2561.525457</v>
+        <v>2187.730908</v>
       </c>
       <c r="F41" t="n">
-        <v>5254</v>
+        <v>13682</v>
       </c>
       <c r="G41" t="n">
-        <v>2970.721241</v>
+        <v>2208.89971</v>
       </c>
       <c r="H41" t="n">
-        <v>78174</v>
+        <v>430083</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8622570000000001</v>
+        <v>0.990417</v>
       </c>
     </row>
     <row r="42">
@@ -1859,27 +1824,27 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TRANSPORTE AQUAVIÁRIO</t>
+          <t>TRANSPORTE TERRESTRE</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3955.271364</v>
+        <v>2561.525457</v>
       </c>
       <c r="F42" t="n">
-        <v>88</v>
+        <v>5254</v>
       </c>
       <c r="G42" t="n">
-        <v>4338.654389</v>
+        <v>2970.721241</v>
       </c>
       <c r="H42" t="n">
-        <v>13136</v>
+        <v>78174</v>
       </c>
       <c r="I42" t="n">
-        <v>0.911636</v>
+        <v>0.8622570000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1894,31 +1859,27 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TRANSPORTE AÉREO</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>TRANSPORTE AQUAVIÁRIO</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3955.271364</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G43" t="n">
-        <v>4460.718377</v>
+        <v>4338.654389</v>
       </c>
       <c r="H43" t="n">
-        <v>2607</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>13136</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.911636</v>
       </c>
     </row>
     <row r="44">
@@ -1933,27 +1894,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>2137.837732</v>
+          <t>TRANSPORTE AÉREO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>3534.911156</v>
+        <v>4460.718377</v>
       </c>
       <c r="H44" t="n">
-        <v>25919</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.604778</v>
+        <v>2607</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1968,62 +1933,62 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
+          <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5678.604872</v>
+        <v>2137.837732</v>
       </c>
       <c r="F45" t="n">
-        <v>273</v>
+        <v>441</v>
       </c>
       <c r="G45" t="n">
-        <v>4263.847585</v>
+        <v>3534.911156</v>
       </c>
       <c r="H45" t="n">
-        <v>8386</v>
+        <v>25919</v>
       </c>
       <c r="I45" t="n">
-        <v>1.331803</v>
+        <v>0.604778</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
+          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ALOJAMENTO</t>
+          <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2033.181171</v>
+        <v>5678.604872</v>
       </c>
       <c r="F46" t="n">
-        <v>444</v>
+        <v>273</v>
       </c>
       <c r="G46" t="n">
-        <v>2071.279973</v>
+        <v>4263.847585</v>
       </c>
       <c r="H46" t="n">
-        <v>16498</v>
+        <v>8386</v>
       </c>
       <c r="I46" t="n">
-        <v>0.981606</v>
+        <v>1.331803</v>
       </c>
     </row>
     <row r="47">
@@ -2038,62 +2003,62 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO</t>
+          <t>ALOJAMENTO</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1834.619018</v>
+        <v>2033.181171</v>
       </c>
       <c r="F47" t="n">
-        <v>1995</v>
+        <v>444</v>
       </c>
       <c r="G47" t="n">
-        <v>1951.585547</v>
+        <v>2071.279973</v>
       </c>
       <c r="H47" t="n">
-        <v>75416</v>
+        <v>16498</v>
       </c>
       <c r="I47" t="n">
-        <v>0.940066</v>
+        <v>0.981606</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
+          <t>ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3021.6255</v>
+        <v>1834.619018</v>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>1995</v>
       </c>
       <c r="G48" t="n">
-        <v>2934.253162</v>
+        <v>1951.585547</v>
       </c>
       <c r="H48" t="n">
-        <v>1034</v>
+        <v>75416</v>
       </c>
       <c r="I48" t="n">
-        <v>1.029777</v>
+        <v>0.940066</v>
       </c>
     </row>
     <row r="49">
@@ -2108,50 +2073,46 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ATIVIDADES CINEMATOGRÁFICAS, PRODUÇÃO DE VÍDEOS E DE PROGRAMAS DE TELEVISÃO; GRAVAÇÃO DE SOM E EDIÇÃO DE MÚSICA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3021.6255</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
-        <v>2252.646755</v>
+        <v>2934.253162</v>
       </c>
       <c r="H49" t="n">
-        <v>943</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1034</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.029777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EXTRAÇÃO DE PETRÓLEO E GÁS NATURAL</t>
+          <t>ATIVIDADES CINEMATOGRÁFICAS, PRODUÇÃO DE VÍDEOS E DE PROGRAMAS DE TELEVISÃO; GRAVAÇÃO DE SOM E EDIÇÃO DE MÚSICA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2163,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>32925.222298</v>
+        <v>2252.646755</v>
       </c>
       <c r="H50" t="n">
-        <v>396</v>
+        <v>943</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2177,36 +2138,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE RÁDIO E DE TELEVISÃO</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1751.37</v>
+          <t>EXTRAÇÃO DE PETRÓLEO E GÁS NATURAL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>3162.036236</v>
+        <v>32925.222298</v>
       </c>
       <c r="H51" t="n">
-        <v>4532</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.553874</v>
+        <v>396</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -2221,27 +2186,27 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TELECOMUNICAÇÕES</t>
+          <t>ATIVIDADES DE RÁDIO E DE TELEVISÃO</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1995.853465</v>
+        <v>1751.37</v>
       </c>
       <c r="F52" t="n">
-        <v>303</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>2673.351948</v>
+        <v>3162.036236</v>
       </c>
       <c r="H52" t="n">
-        <v>15627</v>
+        <v>4532</v>
       </c>
       <c r="I52" t="n">
-        <v>0.746573</v>
+        <v>0.553874</v>
       </c>
     </row>
     <row r="53">
@@ -2256,27 +2221,27 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
+          <t>TELECOMUNICAÇÕES</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2826.544157</v>
+        <v>1995.853465</v>
       </c>
       <c r="F53" t="n">
-        <v>89</v>
+        <v>303</v>
       </c>
       <c r="G53" t="n">
-        <v>3163.328832</v>
+        <v>2673.351948</v>
       </c>
       <c r="H53" t="n">
-        <v>13019</v>
+        <v>15627</v>
       </c>
       <c r="I53" t="n">
-        <v>0.893535</v>
+        <v>0.746573</v>
       </c>
     </row>
     <row r="54">
@@ -2291,62 +2256,62 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
+          <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2044.303471</v>
+        <v>2826.544157</v>
       </c>
       <c r="F54" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="G54" t="n">
-        <v>5692.941871</v>
+        <v>3163.328832</v>
       </c>
       <c r="H54" t="n">
-        <v>2956</v>
+        <v>13019</v>
       </c>
       <c r="I54" t="n">
-        <v>0.359094</v>
+        <v>0.893535</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
+          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
+          <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4586.089698</v>
+        <v>2044.303471</v>
       </c>
       <c r="F55" t="n">
-        <v>1191</v>
+        <v>121</v>
       </c>
       <c r="G55" t="n">
-        <v>9503.110364</v>
+        <v>5692.941871</v>
       </c>
       <c r="H55" t="n">
-        <v>27313</v>
+        <v>2956</v>
       </c>
       <c r="I55" t="n">
-        <v>0.482588</v>
+        <v>0.359094</v>
       </c>
     </row>
     <row r="56">
@@ -2361,31 +2326,27 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SEGUROS, RESSEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4586.089698</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1191</v>
       </c>
       <c r="G56" t="n">
-        <v>4209.189191</v>
+        <v>9503.110364</v>
       </c>
       <c r="H56" t="n">
-        <v>4897</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>27313</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.482588</v>
       </c>
     </row>
     <row r="57">
@@ -2400,171 +2361,175 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2407.7415</v>
+          <t>SEGUROS, RESSEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2386.450794</v>
+        <v>4209.189191</v>
       </c>
       <c r="H57" t="n">
-        <v>3854</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1.008921</v>
+        <v>4897</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2000.954181</v>
+        <v>2407.7415</v>
       </c>
       <c r="F58" t="n">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="G58" t="n">
-        <v>2585.215417</v>
+        <v>2386.450794</v>
       </c>
       <c r="H58" t="n">
-        <v>6664</v>
+        <v>3854</v>
       </c>
       <c r="I58" t="n">
-        <v>0.773999</v>
+        <v>1.008921</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2144.35536</v>
+        <v>2000.954181</v>
       </c>
       <c r="F59" t="n">
-        <v>444</v>
+        <v>299</v>
       </c>
       <c r="G59" t="n">
-        <v>3638.019115</v>
+        <v>2585.215417</v>
       </c>
       <c r="H59" t="n">
-        <v>24467</v>
+        <v>6664</v>
       </c>
       <c r="I59" t="n">
-        <v>0.589429</v>
+        <v>0.773999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EXTRAÇÃO DE MINERAIS METÁLICOS</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2144.35536</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="G60" t="n">
-        <v>7188.166356</v>
+        <v>3638.019115</v>
       </c>
       <c r="H60" t="n">
-        <v>27508</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>24467</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.589429</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1646.763125</v>
+          <t>EXTRAÇÃO DE MINERAIS METÁLICOS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F61" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>3374.77519</v>
+        <v>7188.166356</v>
       </c>
       <c r="H61" t="n">
-        <v>9206</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.487962</v>
+        <v>27508</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -2579,27 +2544,27 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
+          <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2529.909317</v>
+        <v>1646.763125</v>
       </c>
       <c r="F62" t="n">
-        <v>747</v>
+        <v>16</v>
       </c>
       <c r="G62" t="n">
-        <v>2850.958418</v>
+        <v>3374.77519</v>
       </c>
       <c r="H62" t="n">
-        <v>22409</v>
+        <v>9206</v>
       </c>
       <c r="I62" t="n">
-        <v>0.887389</v>
+        <v>0.487962</v>
       </c>
     </row>
     <row r="63">
@@ -2614,31 +2579,27 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PESQUISA E DESENVOLVIMENTO CIENTÍFICO</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2529.909317</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="G63" t="n">
-        <v>12038.756157</v>
+        <v>2850.958418</v>
       </c>
       <c r="H63" t="n">
-        <v>5417</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>22409</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.887389</v>
       </c>
     </row>
     <row r="64">
@@ -2653,27 +2614,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>1719.867214</v>
+          <t>PESQUISA E DESENVOLVIMENTO CIENTÍFICO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F64" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>2257.447342</v>
+        <v>12038.756157</v>
       </c>
       <c r="H64" t="n">
-        <v>3996</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.761864</v>
+        <v>5417</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -2688,27 +2653,27 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3153.283191</v>
+        <v>1719.867214</v>
       </c>
       <c r="F65" t="n">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="G65" t="n">
-        <v>3309.940858</v>
+        <v>2257.447342</v>
       </c>
       <c r="H65" t="n">
-        <v>8039</v>
+        <v>3996</v>
       </c>
       <c r="I65" t="n">
-        <v>0.952671</v>
+        <v>0.761864</v>
       </c>
     </row>
     <row r="66">
@@ -2723,62 +2688,62 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ATIVIDADES VETERINÁRIAS</t>
+          <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2064.477069</v>
+        <v>3153.283191</v>
       </c>
       <c r="F66" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G66" t="n">
-        <v>2080.784772</v>
+        <v>3309.940858</v>
       </c>
       <c r="H66" t="n">
-        <v>1823</v>
+        <v>8039</v>
       </c>
       <c r="I66" t="n">
-        <v>0.992163</v>
+        <v>0.952671</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
+          <t>ATIVIDADES VETERINÁRIAS</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3462.637678</v>
+        <v>2064.477069</v>
       </c>
       <c r="F67" t="n">
-        <v>534</v>
+        <v>58</v>
       </c>
       <c r="G67" t="n">
-        <v>2616.612386</v>
+        <v>2080.784772</v>
       </c>
       <c r="H67" t="n">
-        <v>20860</v>
+        <v>1823</v>
       </c>
       <c r="I67" t="n">
-        <v>1.323328</v>
+        <v>0.992163</v>
       </c>
     </row>
     <row r="68">
@@ -2793,27 +2758,27 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
+          <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2372.4625</v>
+        <v>3462.637678</v>
       </c>
       <c r="F68" t="n">
-        <v>28</v>
+        <v>534</v>
       </c>
       <c r="G68" t="n">
-        <v>2115.523985</v>
+        <v>2616.612386</v>
       </c>
       <c r="H68" t="n">
-        <v>40889</v>
+        <v>20860</v>
       </c>
       <c r="I68" t="n">
-        <v>1.121454</v>
+        <v>1.323328</v>
       </c>
     </row>
     <row r="69">
@@ -2828,97 +2793,97 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
+          <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2419.092388</v>
+        <v>2372.4625</v>
       </c>
       <c r="F69" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="G69" t="n">
-        <v>2318.895316</v>
+        <v>2115.523985</v>
       </c>
       <c r="H69" t="n">
-        <v>2750</v>
+        <v>40889</v>
       </c>
       <c r="I69" t="n">
-        <v>1.043209</v>
+        <v>1.121454</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EXTRAÇÃO DE MINERAIS NÃO-METÁLICOS</t>
+          <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2476.797143</v>
+        <v>2419.092388</v>
       </c>
       <c r="F70" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G70" t="n">
-        <v>3673.862819</v>
+        <v>2318.895316</v>
       </c>
       <c r="H70" t="n">
-        <v>4721</v>
+        <v>2750</v>
       </c>
       <c r="I70" t="n">
-        <v>0.674167</v>
+        <v>1.043209</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
+          <t>EXTRAÇÃO DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2358.557176</v>
+        <v>2476.797143</v>
       </c>
       <c r="F71" t="n">
-        <v>1020</v>
+        <v>35</v>
       </c>
       <c r="G71" t="n">
-        <v>2553.231371</v>
+        <v>3673.862819</v>
       </c>
       <c r="H71" t="n">
-        <v>48092</v>
+        <v>4721</v>
       </c>
       <c r="I71" t="n">
-        <v>0.923754</v>
+        <v>0.674167</v>
       </c>
     </row>
     <row r="72">
@@ -2933,27 +2898,27 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SERVIÇOS PARA EDIFÍCIOS E ATIVIDADES PAISAGÍSTICAS</t>
+          <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2066.085088</v>
+        <v>2358.557176</v>
       </c>
       <c r="F72" t="n">
-        <v>3361</v>
+        <v>1020</v>
       </c>
       <c r="G72" t="n">
-        <v>2045.734362</v>
+        <v>2553.231371</v>
       </c>
       <c r="H72" t="n">
-        <v>79701</v>
+        <v>48092</v>
       </c>
       <c r="I72" t="n">
-        <v>1.009948</v>
+        <v>0.923754</v>
       </c>
     </row>
     <row r="73">
@@ -2968,132 +2933,132 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
+          <t>SERVIÇOS PARA EDIFÍCIOS E ATIVIDADES PAISAGÍSTICAS</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2112.331022</v>
+        <v>2066.085088</v>
       </c>
       <c r="F73" t="n">
-        <v>5666</v>
+        <v>3361</v>
       </c>
       <c r="G73" t="n">
-        <v>2354.890126</v>
+        <v>2045.734362</v>
       </c>
       <c r="H73" t="n">
-        <v>96230</v>
+        <v>79701</v>
       </c>
       <c r="I73" t="n">
-        <v>0.896998</v>
+        <v>1.009948</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3986.473767</v>
+        <v>2112.331022</v>
       </c>
       <c r="F74" t="n">
-        <v>6499</v>
+        <v>5666</v>
       </c>
       <c r="G74" t="n">
-        <v>5903.351765</v>
+        <v>2354.890126</v>
       </c>
       <c r="H74" t="n">
-        <v>1036043</v>
+        <v>96230</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6752899999999999</v>
+        <v>0.896998</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2911.008991</v>
+        <v>3986.473767</v>
       </c>
       <c r="F75" t="n">
-        <v>10498</v>
+        <v>6499</v>
       </c>
       <c r="G75" t="n">
-        <v>5355.117204</v>
+        <v>5903.351765</v>
       </c>
       <c r="H75" t="n">
-        <v>165960</v>
+        <v>1036043</v>
       </c>
       <c r="I75" t="n">
-        <v>0.543594</v>
+        <v>0.6752899999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2764.663675</v>
+        <v>2911.008991</v>
       </c>
       <c r="F76" t="n">
-        <v>2901</v>
+        <v>10498</v>
       </c>
       <c r="G76" t="n">
-        <v>3683.540397</v>
+        <v>5355.117204</v>
       </c>
       <c r="H76" t="n">
-        <v>143825</v>
+        <v>165960</v>
       </c>
       <c r="I76" t="n">
-        <v>0.750545</v>
+        <v>0.543594</v>
       </c>
     </row>
     <row r="77">
@@ -3108,27 +3073,27 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA INTEGRADAS COM ASSISTÊNCIA SOCIAL, PRESTADAS EM RESIDÊNCIAS COLETIVAS E PARTICULARES</t>
+          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2211.863016</v>
+        <v>2764.663675</v>
       </c>
       <c r="F77" t="n">
-        <v>63</v>
+        <v>2901</v>
       </c>
       <c r="G77" t="n">
-        <v>2470.658017</v>
+        <v>3683.540397</v>
       </c>
       <c r="H77" t="n">
-        <v>2426</v>
+        <v>143825</v>
       </c>
       <c r="I77" t="n">
-        <v>0.895253</v>
+        <v>0.750545</v>
       </c>
     </row>
     <row r="78">
@@ -3143,101 +3108,101 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE ASSISTÊNCIA SOCIAL SEM ALOJAMENTO</t>
+          <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA INTEGRADAS COM ASSISTÊNCIA SOCIAL, PRESTADAS EM RESIDÊNCIAS COLETIVAS E PARTICULARES</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3619.62535</v>
+        <v>2211.863016</v>
       </c>
       <c r="F78" t="n">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="G78" t="n">
-        <v>3248.986981</v>
+        <v>2470.658017</v>
       </c>
       <c r="H78" t="n">
-        <v>6916</v>
+        <v>2426</v>
       </c>
       <c r="I78" t="n">
-        <v>1.114078</v>
+        <v>0.895253</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
+          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE APOIO À EXTRAÇÃO DE MINERAIS</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>SERVIÇOS DE ASSISTÊNCIA SOCIAL SEM ALOJAMENTO</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3619.62535</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G79" t="n">
-        <v>12590.02618</v>
+        <v>3248.986981</v>
       </c>
       <c r="H79" t="n">
-        <v>869</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6916</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1.114078</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ATIVIDADES ARTÍSTICAS, CRIATIVAS E DE ESPETÁCULOS</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>5138.89</v>
+          <t>ATIVIDADES DE APOIO À EXTRAÇÃO DE MINERAIS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>4660.874075</v>
+        <v>12590.02618</v>
       </c>
       <c r="H80" t="n">
-        <v>1691</v>
-      </c>
-      <c r="I80" t="n">
-        <v>1.102559</v>
+        <v>869</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -3252,31 +3217,27 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ATIVIDADES LIGADAS AO PATRIMÔNIO CULTURAL E AMBIENTAL</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>ATIVIDADES ARTÍSTICAS, CRIATIVAS E DE ESPETÁCULOS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5138.89</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>8045.512061</v>
+        <v>4660.874075</v>
       </c>
       <c r="H81" t="n">
-        <v>558</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1.102559</v>
       </c>
     </row>
     <row r="82">
@@ -3291,62 +3252,66 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>1753.601166</v>
+          <t>ATIVIDADES LIGADAS AO PATRIMÔNIO CULTURAL E AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F82" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>2005.454891</v>
+        <v>8045.512061</v>
       </c>
       <c r="H82" t="n">
-        <v>12877</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.874416</v>
+        <v>558</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
+          <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2994.593105</v>
+        <v>1753.601166</v>
       </c>
       <c r="F83" t="n">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="G83" t="n">
-        <v>2847.527382</v>
+        <v>2005.454891</v>
       </c>
       <c r="H83" t="n">
-        <v>38076</v>
+        <v>12877</v>
       </c>
       <c r="I83" t="n">
-        <v>1.051647</v>
+        <v>0.874416</v>
       </c>
     </row>
     <row r="84">
@@ -3361,27 +3326,27 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
+          <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2068.817187</v>
+        <v>2994.593105</v>
       </c>
       <c r="F84" t="n">
-        <v>64</v>
+        <v>554</v>
       </c>
       <c r="G84" t="n">
-        <v>2390.923297</v>
+        <v>2847.527382</v>
       </c>
       <c r="H84" t="n">
-        <v>2839</v>
+        <v>38076</v>
       </c>
       <c r="I84" t="n">
-        <v>0.86528</v>
+        <v>1.051647</v>
       </c>
     </row>
     <row r="85">
@@ -3396,85 +3361,81 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
+          <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2287.604458</v>
+        <v>2068.817187</v>
       </c>
       <c r="F85" t="n">
-        <v>323</v>
+        <v>64</v>
       </c>
       <c r="G85" t="n">
-        <v>2145.147677</v>
+        <v>2390.923297</v>
       </c>
       <c r="H85" t="n">
-        <v>10846</v>
+        <v>2839</v>
       </c>
       <c r="I85" t="n">
-        <v>1.066409</v>
+        <v>0.86528</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SERVIÇOS DOMÉSTICOS</t>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SERVIÇOS DOMÉSTICOS</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2287.604458</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="G86" t="n">
-        <v>1765.473529</v>
+        <v>2145.147677</v>
       </c>
       <c r="H86" t="n">
-        <v>17</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10846</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.066409</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
+          <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
+          <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3486,12 +3447,51 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1765.473529</v>
+      </c>
+      <c r="H87" t="n">
+        <v>17</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>99</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
         <v>6810.10122</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H88" t="n">
         <v>41</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/Renda_por_Divisao_CNAE_RAIS_Ananindeua.xlsx
+++ b/Renda_por_Divisao_CNAE_RAIS_Ananindeua.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +32,47 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A5E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2A5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,10 +87,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,3079 +468,3084 @@
   <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>RENDA MÉDIA POR DIVISÃO CNAE (RAIS 2025) — ANANINDEUA vs PARÁ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Vínculos ativos em 31/12, remuneração média nominal do ano (Vl Rem Média Nom). QL Renda = renda Ananindeua / renda Pará.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Nome Seção</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Divisão</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Nome Divisão</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Renda Média Ananindeua (R$)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Vínculos Ananindeua</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Renda Média Pará (R$)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Vínculos Pará</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>QL Renda (Ana/Pa)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="7" t="n">
         <v>1873.45</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>129</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="7" t="n">
         <v>2635.197144</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="7" t="n">
         <v>104286</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="7" t="n">
         <v>0.710934</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS ALIMENTÍCIOS</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="9" t="n">
         <v>2677.349684</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="9" t="n">
         <v>4242</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="9" t="n">
         <v>2641.254964</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="9" t="n">
         <v>89228</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="9" t="n">
         <v>1.013666</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE BEBIDAS</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="7" t="n">
         <v>2545.100909</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="7" t="n">
         <v>3206.446996</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="7" t="n">
         <v>8273</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.793745</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS TÊXTEIS</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="9" t="n">
         <v>1809.07</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="9" t="n">
         <v>2084.118844</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="9" t="n">
         <v>2648</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="9" t="n">
         <v>0.868026</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>CONFECÇÃO DE ARTIGOS DO VESTUÁRIO E ACESSÓRIOS</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="7" t="n">
         <v>1865.38442</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>276</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1828.820862</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>4395</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>1.019993</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>PREPARAÇÃO DE COUROS E FABRICAÇÃO DE ARTEFATOS DE COURO, ARTIGOS PARA VIAGEM E CALÇADOS</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="9" t="n">
         <v>1733.88</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="9" t="n">
         <v>2605.352094</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="9" t="n">
         <v>3476</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="9" t="n">
         <v>0.665507</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS DE MADEIRA</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="7" t="n">
         <v>3087.425007</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>701</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>2492.016059</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>14538</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>1.238927</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE CELULOSE, PAPEL E PRODUTOS DE PAPEL</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="9" t="n">
         <v>2275.328696</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="9" t="n">
         <v>3289.228769</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="9" t="n">
         <v>5247</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="9" t="n">
         <v>0.691751</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>IMPRESSÃO E REPRODUÇÃO DE GRAVAÇÕES</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="7" t="n">
         <v>1964.900385</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>2243.437741</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="7" t="n">
         <v>3595</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="7" t="n">
         <v>0.875844</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE COQUE, DE PRODUTOS DERIVADOS DO PETRÓLEO E DE BIOCOMBUSTÍVEIS</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="9" t="n">
         <v>3290.996721</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="9" t="n">
         <v>122</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="9" t="n">
         <v>4089.675863</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="9" t="n">
         <v>3979</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="9" t="n">
         <v>0.804708</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>PRODUÇÃO FLORESTAL</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="7" t="n">
         <v>4757.2</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="7" t="n">
         <v>2911.558271</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="7" t="n">
         <v>7594</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="7" t="n">
         <v>1.633902</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS QUÍMICOS</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="9" t="n">
         <v>2613.732805</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="9" t="n">
         <v>688</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="9" t="n">
         <v>3660.913293</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="9" t="n">
         <v>8229</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="9" t="n">
         <v>0.713956</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS FARMOQUÍMICOS E FARMACÊUTICOS</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="7" t="n">
         <v>4664.245892</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="7" t="n">
         <v>1346</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS DE BORRACHA E DE MATERIAL PLÁSTICO</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="9" t="n">
         <v>2651.106931</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="9" t="n">
         <v>492</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="9" t="n">
         <v>3375.698749</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="9" t="n">
         <v>18289</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.785351</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="7" t="n">
         <v>2723.266048</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="7" t="n">
         <v>792</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="7" t="n">
         <v>2485.562422</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="7" t="n">
         <v>17071</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="7" t="n">
         <v>1.095634</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>METALURGIA</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="9" t="n">
         <v>2439.49513</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="9" t="n">
         <v>154</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="9" t="n">
         <v>5491.600103</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="9" t="n">
         <v>12798</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="9" t="n">
         <v>0.444223</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS DE METAL, EXCETO MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="7" t="n">
         <v>2650.480317</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="7" t="n">
         <v>221</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="7" t="n">
         <v>3316.442745</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="7" t="n">
         <v>13382</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.799194</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE EQUIPAMENTOS DE INFORMÁTICA, PRODUTOS ELETRÔNICOS E ÓPTICOS</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="9" t="n">
         <v>3941.304626</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="9" t="n">
         <v>30374</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE MÁQUINAS, APARELHOS E MATERIAIS ELÉTRICOS</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="7" t="n">
         <v>2313.619589</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="7" t="n">
         <v>146</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="7" t="n">
         <v>3466.873835</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="7" t="n">
         <v>8352</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="7" t="n">
         <v>0.66735</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="9" t="n">
         <v>3176.86025</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="9" t="n">
         <v>3972.233063</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="9" t="n">
         <v>8459</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="9" t="n">
         <v>0.799767</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE VEÍCULOS AUTOMOTORES, REBOQUES E CARROCERIAS</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="7" t="n">
         <v>2217.898235</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="7" t="n">
         <v>3454.059563</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="7" t="n">
         <v>7374</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="7" t="n">
         <v>0.642113</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="9" t="n">
         <v>2344.143184</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="9" t="n">
         <v>1052</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE OUTROS EQUIPAMENTOS DE TRANSPORTE, EXCETO VEÍCULOS AUTOMOTORES</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="7" t="n">
         <v>3150.448</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" s="7" t="n">
         <v>5135.769229</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="7" t="n">
         <v>24526</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="7" t="n">
         <v>0.613433</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE MÓVEIS</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="9" t="n">
         <v>2155.502051</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="9" t="n">
         <v>590</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" s="9" t="n">
         <v>2475.036147</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="9" t="n">
         <v>6553</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="9" t="n">
         <v>0.870897</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>FABRICAÇÃO DE PRODUTOS DIVERSOS</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="7" t="n">
         <v>1850.134545</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="7" t="n">
         <v>2907.595459</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="7" t="n">
         <v>4787</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="7" t="n">
         <v>0.636311</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>MANUTENÇÃO, REPARAÇÃO E INSTALAÇÃO DE MÁQUINAS E EQUIPAMENTOS</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="9" t="n">
         <v>2754.15576</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="9" t="n">
         <v>3161.418785</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="9" t="n">
         <v>12605</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.871177</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>ELETRICIDADE, GÁS E OUTRAS UTILIDADES</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" s="7" t="n">
         <v>6811.088797</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="7" t="n">
         <v>12905</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>CAPTAÇÃO, TRATAMENTO E DISTRIBUIÇÃO DE ÁGUA</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="9" t="n">
         <v>2536.292381</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="9" t="n">
         <v>4759.262345</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="9" t="n">
         <v>10441</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="9" t="n">
         <v>0.532917</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>ESGOTO E ATIVIDADES RELACIONADAS</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="7" t="n">
         <v>2802.474118</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="7" t="n">
         <v>2640.627046</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="7" t="n">
         <v>457</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="7" t="n">
         <v>1.061291</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>COLETA, TRATAMENTO E DISPOSIÇÃO DE RESÍDUOS; RECUPERAÇÃO DE MATERIAIS</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="9" t="n">
         <v>2763.048652</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="9" t="n">
         <v>1328</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34" s="9" t="n">
         <v>2728.160887</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="9" t="n">
         <v>10973</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="9" t="n">
         <v>1.012788</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DESCONTAMINAÇÃO E OUTROS SERVIÇOS DE GESTÃO DE RESÍDUOS</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35" s="7" t="n">
         <v>2330.951111</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO DE EDIFÍCIOS</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="9" t="n">
         <v>2217.128974</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="9" t="n">
         <v>1667</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" s="9" t="n">
         <v>2478.15883</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="9" t="n">
         <v>53041</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="9" t="n">
         <v>0.894668</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>OBRAS DE INFRA-ESTRUTURA</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="7" t="n">
         <v>3611.458028</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="7" t="n">
         <v>2099</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37" s="7" t="n">
         <v>3563.770881</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="7" t="n">
         <v>59348</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="7" t="n">
         <v>1.013381</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS ESPECIALIZADOS PARA CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="9" t="n">
         <v>2471.714245</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="9" t="n">
         <v>742</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" s="9" t="n">
         <v>2871.449377</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="9" t="n">
         <v>45112</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="9" t="n">
         <v>0.8607900000000001</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO E REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="7" t="n">
         <v>3351.357196</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="7" t="n">
         <v>3278</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" s="7" t="n">
         <v>3029.790097</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="7" t="n">
         <v>69231</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="7" t="n">
         <v>1.106135</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>COMÉRCIO POR ATACADO, EXCETO VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="9" t="n">
         <v>3010.494691</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="9" t="n">
         <v>5133</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" s="9" t="n">
         <v>2935.297564</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="9" t="n">
         <v>109578</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="9" t="n">
         <v>1.025618</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO VAREJISTA</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="7" t="n">
         <v>2187.730908</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="7" t="n">
         <v>13682</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41" s="7" t="n">
         <v>2208.89971</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="7" t="n">
         <v>430083</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="7" t="n">
         <v>0.990417</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE TERRESTRE</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="9" t="n">
         <v>2561.525457</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="9" t="n">
         <v>5254</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" s="9" t="n">
         <v>2970.721241</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="9" t="n">
         <v>78174</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="9" t="n">
         <v>0.8622570000000001</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>TRANSPORTE AQUAVIÁRIO</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="7" t="n">
         <v>3955.271364</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" s="7" t="n">
         <v>4338.654389</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="7" t="n">
         <v>13136</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="7" t="n">
         <v>0.911636</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE AÉREO</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="9" t="n">
         <v>4460.718377</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="9" t="n">
         <v>2607</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>ARMAZENAMENTO E ATIVIDADES AUXILIARES DOS TRANSPORTES</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="7" t="n">
         <v>2137.837732</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="7" t="n">
         <v>441</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="7" t="n">
         <v>3534.911156</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="7" t="n">
         <v>25919</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="7" t="n">
         <v>0.604778</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>CORREIO E OUTRAS ATIVIDADES DE ENTREGA</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="9" t="n">
         <v>5678.604872</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="9" t="n">
         <v>273</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="9" t="n">
         <v>4263.847585</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="9" t="n">
         <v>8386</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="9" t="n">
         <v>1.331803</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="7" t="n">
         <v>2033.181171</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="7" t="n">
         <v>444</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="7" t="n">
         <v>2071.279973</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="7" t="n">
         <v>16498</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="7" t="n">
         <v>0.981606</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="9" t="n">
         <v>1834.619018</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="9" t="n">
         <v>1995</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="9" t="n">
         <v>1951.585547</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="9" t="n">
         <v>75416</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="9" t="n">
         <v>0.940066</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>EDIÇÃO E EDIÇÃO INTEGRADA À IMPRESSÃO</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="7" t="n">
         <v>3021.6255</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="7" t="n">
         <v>2934.253162</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="7" t="n">
         <v>1034</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="7" t="n">
         <v>1.029777</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES CINEMATOGRÁFICAS, PRODUÇÃO DE VÍDEOS E DE PROGRAMAS DE TELEVISÃO; GRAVAÇÃO DE SOM E EDIÇÃO DE MÚSICA</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="9" t="n">
         <v>2252.646755</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="9" t="n">
         <v>943</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>EXTRAÇÃO DE PETRÓLEO E GÁS NATURAL</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="7" t="n">
         <v>32925.222298</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="7" t="n">
         <v>396</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE RÁDIO E DE TELEVISÃO</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="9" t="n">
         <v>1751.37</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="9" t="n">
         <v>3162.036236</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="9" t="n">
         <v>4532</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="9" t="n">
         <v>0.553874</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>TELECOMUNICAÇÕES</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="7" t="n">
         <v>1995.853465</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="7" t="n">
         <v>2673.351948</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="7" t="n">
         <v>15627</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="7" t="n">
         <v>0.746573</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DOS SERVIÇOS DE TECNOLOGIA DA INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="9" t="n">
         <v>2826.544157</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" s="9" t="n">
         <v>3163.328832</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="9" t="n">
         <v>13019</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="9" t="n">
         <v>0.893535</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES DE PRESTAÇÃO DE SERVIÇOS DE INFORMAÇÃO</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="7" t="n">
         <v>2044.303471</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" s="7" t="n">
         <v>5692.941871</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="7" t="n">
         <v>2956</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="7" t="n">
         <v>0.359094</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE SERVIÇOS FINANCEIROS</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="9" t="n">
         <v>4586.089698</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="9" t="n">
         <v>1191</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" s="9" t="n">
         <v>9503.110364</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="9" t="n">
         <v>27313</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="9" t="n">
         <v>0.482588</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>SEGUROS, RESSEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="7" t="n">
         <v>4209.189191</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="7" t="n">
         <v>4897</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES AUXILIARES DOS SERVIÇOS FINANCEIROS, SEGUROS, PREVIDÊNCIA COMPLEMENTAR E PLANOS DE SAÚDE</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="9" t="n">
         <v>2407.7415</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="9" t="n">
         <v>2386.450794</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="9" t="n">
         <v>3854</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="9" t="n">
         <v>1.008921</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="7" t="n">
         <v>2000.954181</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" s="7" t="n">
         <v>299</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="7" t="n">
         <v>2585.215417</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="7" t="n">
         <v>6664</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="7" t="n">
         <v>0.773999</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES JURÍDICAS, DE CONTABILIDADE E DE AUDITORIA</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="9" t="n">
         <v>2144.35536</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" s="9" t="n">
         <v>444</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" s="9" t="n">
         <v>3638.019115</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="9" t="n">
         <v>24467</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60" s="9" t="n">
         <v>0.589429</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>EXTRAÇÃO DE MINERAIS METÁLICOS</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" s="7" t="n">
         <v>7188.166356</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="7" t="n">
         <v>27508</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE SEDES DE EMPRESAS E DE CONSULTORIA EM GESTÃO EMPRESARIAL</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="9" t="n">
         <v>1646.763125</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" s="9" t="n">
         <v>3374.77519</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="9" t="n">
         <v>9206</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62" s="9" t="n">
         <v>0.487962</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>SERVIÇOS DE ARQUITETURA E ENGENHARIA; TESTES E ANÁLISES TÉCNICAS</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="7" t="n">
         <v>2529.909317</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="7" t="n">
         <v>747</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63" s="7" t="n">
         <v>2850.958418</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="7" t="n">
         <v>22409</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63" s="7" t="n">
         <v>0.887389</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="9" t="n">
         <v>72</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>PESQUISA E DESENVOLVIMENTO CIENTÍFICO</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64" s="9" t="n">
         <v>12038.756157</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="9" t="n">
         <v>5417</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>PUBLICIDADE E PESQUISA DE MERCADO</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="7" t="n">
         <v>1719.867214</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" s="7" t="n">
         <v>2257.447342</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="7" t="n">
         <v>3996</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65" s="7" t="n">
         <v>0.761864</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="9" t="n">
         <v>3153.283191</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66" s="9" t="n">
         <v>3309.940858</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="9" t="n">
         <v>8039</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66" s="9" t="n">
         <v>0.952671</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES VETERINÁRIAS</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="7" t="n">
         <v>2064.477069</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" s="7" t="n">
         <v>2080.784772</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="7" t="n">
         <v>1823</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" s="7" t="n">
         <v>0.992163</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>ALUGUÉIS NÃO-IMOBILIÁRIOS E GESTÃO DE ATIVOS INTANGÍVEIS NÃO-FINANCEIROS</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="9" t="n">
         <v>3462.637678</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="9" t="n">
         <v>534</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" s="9" t="n">
         <v>2616.612386</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="9" t="n">
         <v>20860</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68" s="9" t="n">
         <v>1.323328</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>SELEÇÃO, AGENCIAMENTO E LOCAÇÃO DE MÃO-DE-OBRA</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="7" t="n">
         <v>2372.4625</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69" s="7" t="n">
         <v>2115.523985</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="7" t="n">
         <v>40889</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69" s="7" t="n">
         <v>1.121454</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>AGÊNCIAS DE VIAGENS, OPERADORES TURÍSTICOS E SERVIÇOS DE RESERVAS</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="9" t="n">
         <v>2419.092388</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" s="9" t="n">
         <v>2318.895316</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="9" t="n">
         <v>2750</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70" s="9" t="n">
         <v>1.043209</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>EXTRAÇÃO DE MINERAIS NÃO-METÁLICOS</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="7" t="n">
         <v>2476.797143</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71" s="7" t="n">
         <v>3673.862819</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="7" t="n">
         <v>4721</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" s="7" t="n">
         <v>0.674167</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE VIGILÂNCIA, SEGURANÇA E INVESTIGAÇÃO</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="9" t="n">
         <v>2358.557176</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="9" t="n">
         <v>1020</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="9" t="n">
         <v>2553.231371</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="9" t="n">
         <v>48092</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="9" t="n">
         <v>0.923754</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>SERVIÇOS PARA EDIFÍCIOS E ATIVIDADES PAISAGÍSTICAS</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="7" t="n">
         <v>2066.085088</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="7" t="n">
         <v>3361</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" s="7" t="n">
         <v>2045.734362</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="7" t="n">
         <v>79701</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="7" t="n">
         <v>1.009948</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DE ESCRITÓRIO, DE APOIO ADMINISTRATIVO E OUTROS SERVIÇOS PRESTADOS PRINCIPALMENTE ÀS EMPRESAS</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="9" t="n">
         <v>2112.331022</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="9" t="n">
         <v>5666</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" s="9" t="n">
         <v>2354.890126</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="9" t="n">
         <v>96230</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="9" t="n">
         <v>0.896998</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="7" t="n">
         <v>3986.473767</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" s="7" t="n">
         <v>6499</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75" s="7" t="n">
         <v>5903.351765</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="7" t="n">
         <v>1036043</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="7" t="n">
         <v>0.6752899999999999</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="9" t="n">
         <v>2911.008991</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" s="9" t="n">
         <v>10498</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76" s="9" t="n">
         <v>5355.117204</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="9" t="n">
         <v>165960</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76" s="9" t="n">
         <v>0.543594</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="7" t="n">
         <v>2764.663675</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" s="7" t="n">
         <v>2901</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" s="7" t="n">
         <v>3683.540397</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="7" t="n">
         <v>143825</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77" s="7" t="n">
         <v>0.750545</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE ATENÇÃO À SAÚDE HUMANA INTEGRADAS COM ASSISTÊNCIA SOCIAL, PRESTADAS EM RESIDÊNCIAS COLETIVAS E PARTICULARES</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="9" t="n">
         <v>2211.863016</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78" s="9" t="n">
         <v>2470.658017</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="9" t="n">
         <v>2426</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78" s="9" t="n">
         <v>0.895253</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="7" t="n">
         <v>88</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>SERVIÇOS DE ASSISTÊNCIA SOCIAL SEM ALOJAMENTO</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="7" t="n">
         <v>3619.62535</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" s="7" t="n">
         <v>3248.986981</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="7" t="n">
         <v>6916</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" s="7" t="n">
         <v>1.114078</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE APOIO À EXTRAÇÃO DE MINERAIS</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F80" t="n">
+      <c r="F80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80" s="9" t="n">
         <v>12590.02618</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="9" t="n">
         <v>869</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES ARTÍSTICAS, CRIATIVAS E DE ESPETÁCULOS</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="7" t="n">
         <v>5138.89</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81" s="7" t="n">
         <v>4660.874075</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="7" t="n">
         <v>1691</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" s="7" t="n">
         <v>1.102559</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES LIGADAS AO PATRIMÔNIO CULTURAL E AMBIENTAL</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F82" t="n">
+      <c r="F82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82" s="9" t="n">
         <v>8045.512061</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="9" t="n">
         <v>558</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES ESPORTIVAS E DE RECREAÇÃO E LAZER</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="7" t="n">
         <v>1753.601166</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83" s="7" t="n">
         <v>523</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83" s="7" t="n">
         <v>2005.454891</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83" s="7" t="n">
         <v>12877</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83" s="7" t="n">
         <v>0.874416</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES DE ORGANIZAÇÕES ASSOCIATIVAS</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="9" t="n">
         <v>2994.593105</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="9" t="n">
         <v>554</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84" s="9" t="n">
         <v>2847.527382</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84" s="9" t="n">
         <v>38076</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84" s="9" t="n">
         <v>1.051647</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>REPARAÇÃO E MANUTENÇÃO DE EQUIPAMENTOS DE INFORMÁTICA E COMUNICAÇÃO E DE OBJETOS PESSOAIS E DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="7" t="n">
         <v>2068.817187</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85" s="7" t="n">
         <v>2390.923297</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85" s="7" t="n">
         <v>2839</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85" s="7" t="n">
         <v>0.86528</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS PESSOAIS</t>
         </is>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="9" t="n">
         <v>2287.604458</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="9" t="n">
         <v>323</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="9" t="n">
         <v>2145.147677</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="9" t="n">
         <v>10846</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="9" t="n">
         <v>1.066409</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" s="7" t="n">
         <v>1765.473529</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="F88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88" s="9" t="n">
         <v>6810.10122</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>